--- a/Wikidata Delta/uk_gen_excels/pep_uk_living_relevant_rca_lookup.xlsx
+++ b/Wikidata Delta/uk_gen_excels/pep_uk_living_relevant_rca_lookup.xlsx
@@ -1,26 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet sheetId="1" name="Worksheet" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="202">
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>customer_id</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>RCA Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>RCA ID</t>
+    </r>
   </si>
   <si>
     <t>Lillian Smith</t>
@@ -626,16 +635,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -644,28 +650,37 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -955,14 +970,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:B101"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -970,7 +985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -978,7 +993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -986,7 +1001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -994,7 +1009,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1002,7 +1017,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1010,7 +1025,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1018,7 +1033,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1026,7 +1041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1034,7 +1049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1042,7 +1057,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1050,7 +1065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1058,7 +1073,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1066,7 +1081,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1074,7 +1089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1082,7 +1097,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1090,7 +1105,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1098,7 +1113,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1106,7 +1121,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1114,7 +1129,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1122,7 +1137,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1130,7 +1145,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -1138,7 +1153,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -1146,7 +1161,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -1154,7 +1169,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -1162,7 +1177,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1170,7 +1185,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -1178,7 +1193,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -1186,7 +1201,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -1194,7 +1209,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -1202,7 +1217,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -1210,7 +1225,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -1218,7 +1233,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -1226,7 +1241,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -1234,7 +1249,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -1242,7 +1257,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1250,7 +1265,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -1258,7 +1273,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -1266,7 +1281,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -1274,7 +1289,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -1282,7 +1297,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -1290,7 +1305,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -1298,7 +1313,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -1306,7 +1321,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -1314,7 +1329,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -1322,7 +1337,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -1330,7 +1345,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>92</v>
       </c>
@@ -1338,7 +1353,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -1346,7 +1361,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>96</v>
       </c>
@@ -1354,7 +1369,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1362,7 +1377,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -1370,7 +1385,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>102</v>
       </c>
@@ -1378,7 +1393,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1386,7 +1401,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>106</v>
       </c>
@@ -1394,7 +1409,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -1402,7 +1417,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>110</v>
       </c>
@@ -1410,7 +1425,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -1418,7 +1433,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -1426,7 +1441,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -1434,7 +1449,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -1442,7 +1457,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -1450,7 +1465,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -1458,7 +1473,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>124</v>
       </c>
@@ -1466,7 +1481,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -1474,7 +1489,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>128</v>
       </c>
@@ -1482,7 +1497,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>130</v>
       </c>
@@ -1490,7 +1505,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>132</v>
       </c>
@@ -1498,7 +1513,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>134</v>
       </c>
@@ -1506,7 +1521,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>136</v>
       </c>
@@ -1514,7 +1529,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>138</v>
       </c>
@@ -1522,7 +1537,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>140</v>
       </c>
@@ -1530,7 +1545,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>142</v>
       </c>
@@ -1538,7 +1553,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>144</v>
       </c>
@@ -1546,7 +1561,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>146</v>
       </c>
@@ -1554,7 +1569,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>148</v>
       </c>
@@ -1562,7 +1577,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>150</v>
       </c>
@@ -1570,7 +1585,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>152</v>
       </c>
@@ -1578,7 +1593,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>154</v>
       </c>
@@ -1586,7 +1601,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>156</v>
       </c>
@@ -1594,7 +1609,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>158</v>
       </c>
@@ -1602,7 +1617,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>160</v>
       </c>
@@ -1610,7 +1625,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>162</v>
       </c>
@@ -1618,7 +1633,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>164</v>
       </c>
@@ -1626,7 +1641,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>166</v>
       </c>
@@ -1634,7 +1649,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>168</v>
       </c>
@@ -1642,7 +1657,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>170</v>
       </c>
@@ -1650,7 +1665,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>172</v>
       </c>
@@ -1658,7 +1673,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>174</v>
       </c>
@@ -1666,7 +1681,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>176</v>
       </c>
@@ -1674,7 +1689,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>178</v>
       </c>
@@ -1682,7 +1697,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>180</v>
       </c>
@@ -1690,7 +1705,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>182</v>
       </c>
@@ -1698,7 +1713,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>184</v>
       </c>
@@ -1706,7 +1721,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>186</v>
       </c>
@@ -1714,7 +1729,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>188</v>
       </c>
@@ -1722,7 +1737,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>190</v>
       </c>
@@ -1730,7 +1745,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -1738,7 +1753,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>194</v>
       </c>
@@ -1746,7 +1761,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>196</v>
       </c>
@@ -1754,7 +1769,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>198</v>
       </c>
@@ -1762,7 +1777,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>200</v>
       </c>
@@ -1771,17 +1786,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup paperSize="1" orientation="default" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>